--- a/artfynd/A 38196-2025 artfynd.xlsx
+++ b/artfynd/A 38196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127608635</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127608969</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127608553</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127608978</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127609114</v>
       </c>
       <c r="B6" t="n">
-        <v>80993</v>
+        <v>80995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127609143</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38196-2025 artfynd.xlsx
+++ b/artfynd/A 38196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127608635</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127608969</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127608553</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127608978</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127609114</v>
       </c>
       <c r="B6" t="n">
-        <v>80995</v>
+        <v>80998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127609143</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38196-2025 artfynd.xlsx
+++ b/artfynd/A 38196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127608635</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127608969</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127608553</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127608978</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127609114</v>
       </c>
       <c r="B6" t="n">
-        <v>80998</v>
+        <v>81004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127609143</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38196-2025 artfynd.xlsx
+++ b/artfynd/A 38196-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127608635</v>
+        <v>127609114</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486895</v>
+        <v>486823</v>
       </c>
       <c r="R2" t="n">
-        <v>6835619</v>
+        <v>6835699</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127608969</v>
+        <v>127608553</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486842</v>
+        <v>486923</v>
       </c>
       <c r="R3" t="n">
-        <v>6835694</v>
+        <v>6835531</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127608553</v>
+        <v>127608635</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486923</v>
+        <v>486895</v>
       </c>
       <c r="R4" t="n">
-        <v>6835531</v>
+        <v>6835619</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127608978</v>
+        <v>127608969</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486833</v>
+        <v>486842</v>
       </c>
       <c r="R5" t="n">
-        <v>6835697</v>
+        <v>6835694</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127609114</v>
+        <v>127608978</v>
       </c>
       <c r="B6" t="n">
-        <v>81004</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486823</v>
+        <v>486833</v>
       </c>
       <c r="R6" t="n">
-        <v>6835699</v>
+        <v>6835697</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,11 +1163,11 @@
         <v>127609143</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/artfynd/A 38196-2025 artfynd.xlsx
+++ b/artfynd/A 38196-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127609114</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608553</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608969</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127608978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127609143</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>